--- a/01_Python/20-Pandas/Country GDP Analysis- project/data.xlsx
+++ b/01_Python/20-Pandas/Country GDP Analysis- project/data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="96" yWindow="132" windowWidth="22932" windowHeight="9240"/>
+    <workbookView xWindow="90" yWindow="135" windowWidth="20730" windowHeight="9240"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -2039,14 +2039,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E196"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="28.88671875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="11.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.44140625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="12.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21.109375" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="8.88671875" style="1"/>
+    <col min="1" max="1" width="28.85546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.42578125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="12.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
